--- a/artfynd/A 14339-2026 artfynd.xlsx
+++ b/artfynd/A 14339-2026 artfynd.xlsx
@@ -6045,7 +6045,7 @@
         <v>136269756</v>
       </c>
       <c r="B48" t="n">
-        <v>57184</v>
+        <v>57186</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
